--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
